--- a/Penalestesting.xlsx
+++ b/Penalestesting.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentinzuppa/Desktop/ITBA FUTURE DAY/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AB17D4-01D1-0447-A3CD-D4A743346ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="16">
   <si>
     <t>#</t>
   </si>
@@ -60,56 +69,62 @@
   <si>
     <t>Izquierdo</t>
   </si>
-  <si>
-    <t>NO ES CLARO</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF473821"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFC6DBE1"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFE5E5E5"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -119,7 +134,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -135,7 +150,13 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
@@ -149,6 +170,7 @@
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -163,156 +185,101 @@
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="2" pivot="0" name="Hoja 1-style">
-      <tableStyleElement dxfId="1" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
+    <tableStyle name="Hoja 1-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="E2:J149" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="E2:J149" headerRowCount="0">
   <tableColumns count="6">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
-    <tableColumn name="Column5" id="5"/>
-    <tableColumn name="Column6" id="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Column4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Column5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Column6"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -502,23 +469,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J149"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="17.0"/>
-    <col customWidth="1" min="5" max="5" width="23.63"/>
-    <col customWidth="1" min="6" max="6" width="17.13"/>
-    <col customWidth="1" min="7" max="7" width="15.88"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,21 +517,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E2" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>10</v>
@@ -577,21 +547,21 @@
       </c>
       <c r="J2" s="11"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E3" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>12</v>
@@ -607,21 +577,21 @@
       </c>
       <c r="J3" s="14"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E4" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>12</v>
@@ -635,23 +605,23 @@
       <c r="I4" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J4" s="15"/>
-    </row>
-    <row r="5">
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E5" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>10</v>
@@ -665,23 +635,23 @@
       <c r="I5" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="16"/>
-    </row>
-    <row r="6">
+      <c r="J5" s="15"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>12</v>
@@ -695,23 +665,23 @@
       <c r="I6" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="15"/>
-    </row>
-    <row r="7">
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>12</v>
@@ -727,21 +697,21 @@
       </c>
       <c r="J7" s="14"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>12</v>
@@ -755,23 +725,23 @@
       <c r="I8" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="15"/>
-    </row>
-    <row r="9">
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E9" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>12</v>
@@ -787,21 +757,21 @@
       </c>
       <c r="J9" s="14"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>12</v>
@@ -815,23 +785,23 @@
       <c r="I10" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11">
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>12</v>
@@ -847,21 +817,21 @@
       </c>
       <c r="J11" s="14"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E12" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>12</v>
@@ -875,23 +845,23 @@
       <c r="I12" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="15"/>
-    </row>
-    <row r="13">
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E13" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>10</v>
@@ -905,23 +875,23 @@
       <c r="I13" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="J13" s="16"/>
-    </row>
-    <row r="14">
+      <c r="J13" s="15"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E14" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>12</v>
@@ -935,26 +905,26 @@
       <c r="I14" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="15"/>
-    </row>
-    <row r="15">
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G15" s="13" t="b">
         <v>0</v>
@@ -965,23 +935,23 @@
       <c r="I15" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16">
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E16" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>12</v>
@@ -995,23 +965,23 @@
       <c r="I16" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J16" s="15"/>
-    </row>
-    <row r="17">
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>10</v>
@@ -1025,23 +995,23 @@
       <c r="I17" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18">
+      <c r="J17" s="15"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E18" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>12</v>
@@ -1055,23 +1025,23 @@
       <c r="I18" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19">
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E19" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>12</v>
@@ -1087,21 +1057,21 @@
       </c>
       <c r="J19" s="14"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E20" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>10</v>
@@ -1115,23 +1085,23 @@
       <c r="I20" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21">
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E21" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>12</v>
@@ -1147,24 +1117,24 @@
       </c>
       <c r="J21" s="14"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B22" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E22" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>12</v>
       </c>
       <c r="G22" s="10" t="b">
         <v>0</v>
@@ -1175,26 +1145,26 @@
       <c r="I22" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J22" s="19"/>
-    </row>
-    <row r="23">
+      <c r="J22" s="17"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="7">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B23" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E23" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G23" s="13" t="b">
         <v>0</v>
@@ -1205,23 +1175,23 @@
       <c r="I23" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="J23" s="17"/>
-    </row>
-    <row r="24">
+      <c r="J23" s="16"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B24" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E24" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>12</v>
@@ -1235,23 +1205,23 @@
       <c r="I24" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25">
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="7">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B25" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E25" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>12</v>
@@ -1267,21 +1237,21 @@
       </c>
       <c r="J25" s="14"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B26" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E26" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>10</v>
@@ -1295,23 +1265,23 @@
       <c r="I26" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27">
+      <c r="J26" s="11"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B27" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E27" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>12</v>
@@ -1327,21 +1297,21 @@
       </c>
       <c r="J27" s="14"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="7">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B28" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E28" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>12</v>
@@ -1355,23 +1325,23 @@
       <c r="I28" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29">
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B29" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E29" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>12</v>
@@ -1387,21 +1357,21 @@
       </c>
       <c r="J29" s="14"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="7">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B30" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D30" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E30" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>12</v>
@@ -1415,23 +1385,23 @@
       <c r="I30" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31">
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="7">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B31" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E31" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>12</v>
@@ -1447,21 +1417,21 @@
       </c>
       <c r="J31" s="14"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B32" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E32" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>10</v>
@@ -1475,23 +1445,23 @@
       <c r="I32" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J32" s="18"/>
-    </row>
-    <row r="33">
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="7">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B33" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E33" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>12</v>
@@ -1507,21 +1477,21 @@
       </c>
       <c r="J33" s="14"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="B34" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E34" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>12</v>
@@ -1535,23 +1505,23 @@
       <c r="I34" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35">
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="B35" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E35" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>12</v>
@@ -1567,21 +1537,21 @@
       </c>
       <c r="J35" s="14"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="B36" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D36" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E36" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>12</v>
@@ -1595,23 +1565,23 @@
       <c r="I36" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J36" s="15"/>
-    </row>
-    <row r="37">
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="B37" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D37" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E37" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>12</v>
@@ -1627,21 +1597,21 @@
       </c>
       <c r="J37" s="14"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="B38" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E38" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>12</v>
@@ -1655,23 +1625,23 @@
       <c r="I38" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J38" s="15"/>
-    </row>
-    <row r="39">
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B39" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D39" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E39" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>12</v>
@@ -1687,21 +1657,21 @@
       </c>
       <c r="J39" s="14"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="7">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="B40" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D40" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E40" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>12</v>
@@ -1715,23 +1685,23 @@
       <c r="I40" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41">
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="7">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="B41" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E41" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>12</v>
@@ -1747,21 +1717,21 @@
       </c>
       <c r="J41" s="14"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="7">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="B42" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E42" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>12</v>
@@ -1775,23 +1745,23 @@
       <c r="I42" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43">
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="7">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="B43" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E43" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>12</v>
@@ -1807,21 +1777,21 @@
       </c>
       <c r="J43" s="14"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="7">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="B44" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E44" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>12</v>
@@ -1835,23 +1805,23 @@
       <c r="I44" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45">
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="7">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="B45" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E45" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>12</v>
@@ -1867,21 +1837,21 @@
       </c>
       <c r="J45" s="14"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="B46" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E46" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>12</v>
@@ -1895,25 +1865,25 @@
       <c r="I46" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47">
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="7">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="B47" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E47" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="F47" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="13" t="b">
@@ -1925,23 +1895,23 @@
       <c r="I47" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="J47" s="17"/>
-    </row>
-    <row r="48">
+      <c r="J47" s="16"/>
+    </row>
+    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="7">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="B48" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E48" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>12</v>
@@ -1955,23 +1925,23 @@
       <c r="I48" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J48" s="15"/>
-    </row>
-    <row r="49">
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="7">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="B49" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D49" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E49" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>12</v>
@@ -1987,21 +1957,21 @@
       </c>
       <c r="J49" s="14"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="7">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="B50" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E50" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>12</v>
@@ -2015,23 +1985,23 @@
       <c r="I50" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51">
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A51" s="7">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="B51" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E51" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>12</v>
@@ -2047,21 +2017,21 @@
       </c>
       <c r="J51" s="14"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="7">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="B52" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E52" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>10</v>
@@ -2075,23 +2045,23 @@
       <c r="I52" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J52" s="18"/>
-    </row>
-    <row r="53">
+      <c r="J52" s="11"/>
+    </row>
+    <row r="53" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="7">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="B53" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D53" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E53" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>12</v>
@@ -2107,21 +2077,21 @@
       </c>
       <c r="J53" s="14"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="7">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="B54" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D54" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E54" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>10</v>
@@ -2135,25 +2105,25 @@
       <c r="I54" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J54" s="18"/>
-    </row>
-    <row r="55">
+      <c r="J54" s="11"/>
+    </row>
+    <row r="55" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="7">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="B55" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E55" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="F55" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="12" t="s">
         <v>12</v>
       </c>
       <c r="G55" s="13" t="b">
@@ -2165,23 +2135,23 @@
       <c r="I55" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="J55" s="17"/>
-    </row>
-    <row r="56">
+      <c r="J55" s="16"/>
+    </row>
+    <row r="56" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A56" s="7">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="B56" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E56" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>12</v>
@@ -2195,23 +2165,23 @@
       <c r="I56" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J56" s="15"/>
-    </row>
-    <row r="57">
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A57" s="7">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="B57" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D57" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E57" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>12</v>
@@ -2227,21 +2197,21 @@
       </c>
       <c r="J57" s="14"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A58" s="7">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="B58" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D58" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E58" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>10</v>
@@ -2255,23 +2225,23 @@
       <c r="I58" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="J58" s="18"/>
-    </row>
-    <row r="59">
+      <c r="J58" s="11"/>
+    </row>
+    <row r="59" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A59" s="7">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="B59" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D59" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E59" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>12</v>
@@ -2287,23 +2257,23 @@
       </c>
       <c r="J59" s="14"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A60" s="7">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="B60" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E60" s="8">
-        <v>3.0</v>
-      </c>
-      <c r="F60" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="9" t="s">
         <v>10</v>
       </c>
       <c r="G60" s="10" t="b">
@@ -2315,23 +2285,23 @@
       <c r="I60" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J60" s="19"/>
-    </row>
-    <row r="61">
+      <c r="J60" s="17"/>
+    </row>
+    <row r="61" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A61" s="7">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="B61" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E61" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F61" s="12" t="s">
         <v>12</v>
@@ -2347,21 +2317,21 @@
       </c>
       <c r="J61" s="14"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A62" s="7">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="B62" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E62" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>12</v>
@@ -2375,23 +2345,23 @@
       <c r="I62" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J62" s="15"/>
-    </row>
-    <row r="63">
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A63" s="7">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="B63" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E63" s="8">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>12</v>
@@ -2407,21 +2377,21 @@
       </c>
       <c r="J63" s="14"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A64" s="7">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="B64" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="7">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E64" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>12</v>
@@ -2435,23 +2405,23 @@
       <c r="I64" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J64" s="15"/>
-    </row>
-    <row r="65">
+      <c r="J64" s="3"/>
+    </row>
+    <row r="65" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A65" s="7">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="B65" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E65" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>12</v>
@@ -2467,21 +2437,21 @@
       </c>
       <c r="J65" s="14"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A66" s="7">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="B66" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E66" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>12</v>
@@ -2495,23 +2465,23 @@
       <c r="I66" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="J66" s="15"/>
-    </row>
-    <row r="67">
+      <c r="J66" s="3"/>
+    </row>
+    <row r="67" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A67" s="7">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="B67" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E67" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>12</v>
@@ -2527,21 +2497,21 @@
       </c>
       <c r="J67" s="14"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A68" s="7">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="B68" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C68" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E68" s="23">
-        <v>1.0</v>
+        <v>4</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="18">
+        <v>2</v>
+      </c>
+      <c r="E68" s="19">
+        <v>1</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>12</v>
@@ -2552,26 +2522,26 @@
       <c r="H68" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I68" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" s="25"/>
-    </row>
-    <row r="69">
+      <c r="I68" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" s="14"/>
+    </row>
+    <row r="69" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A69" s="7">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="B69" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E69" s="23">
-        <v>1.0</v>
+        <v>4</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="18">
+        <v>2</v>
+      </c>
+      <c r="E69" s="19">
+        <v>1</v>
       </c>
       <c r="F69" s="13" t="s">
         <v>12</v>
@@ -2582,26 +2552,26 @@
       <c r="H69" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I69" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" s="25"/>
-    </row>
-    <row r="70">
+      <c r="I69" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" s="14"/>
+    </row>
+    <row r="70" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A70" s="7">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="B70" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C70" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E70" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="18">
+        <v>3</v>
+      </c>
+      <c r="E70" s="19">
+        <v>2</v>
       </c>
       <c r="F70" s="13" t="s">
         <v>12</v>
@@ -2612,26 +2582,26 @@
       <c r="H70" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I70" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" s="25"/>
-    </row>
-    <row r="71">
+      <c r="I70" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" s="14"/>
+    </row>
+    <row r="71" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A71" s="7">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="B71" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E71" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="18">
+        <v>4</v>
+      </c>
+      <c r="E71" s="19">
+        <v>2</v>
       </c>
       <c r="F71" s="13" t="s">
         <v>12</v>
@@ -2642,26 +2612,26 @@
       <c r="H71" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I71" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J71" s="25"/>
-    </row>
-    <row r="72">
+      <c r="I71" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" s="14"/>
+    </row>
+    <row r="72" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A72" s="7">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="B72" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C72" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E72" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="18">
+        <v>3</v>
+      </c>
+      <c r="E72" s="19">
+        <v>2</v>
       </c>
       <c r="F72" s="13" t="s">
         <v>10</v>
@@ -2672,26 +2642,26 @@
       <c r="H72" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I72" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" s="25"/>
-    </row>
-    <row r="73">
+      <c r="I72" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" s="14"/>
+    </row>
+    <row r="73" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A73" s="7">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="B73" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C73" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E73" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="18">
+        <v>4</v>
+      </c>
+      <c r="E73" s="19">
+        <v>2</v>
       </c>
       <c r="F73" s="13" t="s">
         <v>10</v>
@@ -2702,26 +2672,26 @@
       <c r="H73" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I73" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" s="25"/>
-    </row>
-    <row r="74">
+      <c r="I73" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" s="14"/>
+    </row>
+    <row r="74" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A74" s="7">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="B74" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C74" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E74" s="23">
-        <v>3.0</v>
+        <v>4</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="18">
+        <v>4</v>
+      </c>
+      <c r="E74" s="19">
+        <v>3</v>
       </c>
       <c r="F74" s="13" t="s">
         <v>10</v>
@@ -2732,26 +2702,26 @@
       <c r="H74" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I74" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" s="25"/>
-    </row>
-    <row r="75">
+      <c r="I74" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" s="14"/>
+    </row>
+    <row r="75" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A75" s="7">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="B75" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C75" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E75" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="18">
+        <v>4</v>
+      </c>
+      <c r="E75" s="19">
+        <v>2</v>
       </c>
       <c r="F75" s="13" t="s">
         <v>12</v>
@@ -2762,26 +2732,26 @@
       <c r="H75" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I75" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" s="25"/>
-    </row>
-    <row r="76">
+      <c r="I75" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" s="14"/>
+    </row>
+    <row r="76" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A76" s="7">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="B76" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C76" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E76" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="18">
+        <v>3</v>
+      </c>
+      <c r="E76" s="19">
+        <v>2</v>
       </c>
       <c r="F76" s="13" t="s">
         <v>12</v>
@@ -2792,26 +2762,26 @@
       <c r="H76" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I76" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" s="25"/>
-    </row>
-    <row r="77">
+      <c r="I76" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" s="14"/>
+    </row>
+    <row r="77" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A77" s="7">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="B77" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C77" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D77" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E77" s="23">
-        <v>1.0</v>
+      <c r="D77" s="18">
+        <v>3</v>
+      </c>
+      <c r="E77" s="19">
+        <v>1</v>
       </c>
       <c r="F77" s="13" t="s">
         <v>10</v>
@@ -2822,26 +2792,26 @@
       <c r="H77" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I77" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" s="25"/>
-    </row>
-    <row r="78">
+      <c r="I77" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" s="14"/>
+    </row>
+    <row r="78" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A78" s="7">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="B78" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C78" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D78" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E78" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="18">
+        <v>2</v>
+      </c>
+      <c r="E78" s="19">
+        <v>2</v>
       </c>
       <c r="F78" s="13" t="s">
         <v>10</v>
@@ -2852,26 +2822,26 @@
       <c r="H78" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I78" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" s="25"/>
-    </row>
-    <row r="79">
+      <c r="I78" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A79" s="7">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="B79" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C79" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D79" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E79" s="23">
-        <v>2.0</v>
+      <c r="D79" s="18">
+        <v>3</v>
+      </c>
+      <c r="E79" s="19">
+        <v>2</v>
       </c>
       <c r="F79" s="13" t="s">
         <v>10</v>
@@ -2882,26 +2852,26 @@
       <c r="H79" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I79" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" s="25"/>
-    </row>
-    <row r="80">
+      <c r="I79" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" s="14"/>
+    </row>
+    <row r="80" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A80" s="7">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="B80" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C80" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E80" s="23">
-        <v>3.0</v>
+        <v>4</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="18">
+        <v>3</v>
+      </c>
+      <c r="E80" s="19">
+        <v>3</v>
       </c>
       <c r="F80" s="13" t="s">
         <v>12</v>
@@ -2912,26 +2882,26 @@
       <c r="H80" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I80" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" s="25"/>
-    </row>
-    <row r="81">
+      <c r="I80" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" s="14"/>
+    </row>
+    <row r="81" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A81" s="7">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="B81" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C81" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E81" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="18">
+        <v>3</v>
+      </c>
+      <c r="E81" s="19">
+        <v>2</v>
       </c>
       <c r="F81" s="13" t="s">
         <v>12</v>
@@ -2942,26 +2912,26 @@
       <c r="H81" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I81" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" s="25"/>
-    </row>
-    <row r="82">
+      <c r="I81" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" s="14"/>
+    </row>
+    <row r="82" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A82" s="7">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="B82" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C82" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E82" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="18">
+        <v>3</v>
+      </c>
+      <c r="E82" s="19">
+        <v>2</v>
       </c>
       <c r="F82" s="13" t="s">
         <v>10</v>
@@ -2972,26 +2942,26 @@
       <c r="H82" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I82" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J82" s="25"/>
-    </row>
-    <row r="83">
+      <c r="I82" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" s="14"/>
+    </row>
+    <row r="83" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A83" s="7">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="B83" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C83" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E83" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="18">
+        <v>3</v>
+      </c>
+      <c r="E83" s="19">
+        <v>2</v>
       </c>
       <c r="F83" s="13" t="s">
         <v>10</v>
@@ -3002,26 +2972,26 @@
       <c r="H83" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I83" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" s="25"/>
-    </row>
-    <row r="84">
+      <c r="I83" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" s="14"/>
+    </row>
+    <row r="84" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A84" s="7">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="B84" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C84" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D84" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E84" s="23">
-        <v>2.0</v>
+      <c r="D84" s="18">
+        <v>4</v>
+      </c>
+      <c r="E84" s="19">
+        <v>2</v>
       </c>
       <c r="F84" s="13" t="s">
         <v>10</v>
@@ -3032,26 +3002,26 @@
       <c r="H84" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I84" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" s="25"/>
-    </row>
-    <row r="85">
+      <c r="I84" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" s="14"/>
+    </row>
+    <row r="85" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A85" s="7">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="B85" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C85" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E85" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="18">
+        <v>3</v>
+      </c>
+      <c r="E85" s="19">
+        <v>2</v>
       </c>
       <c r="F85" s="13" t="s">
         <v>12</v>
@@ -3062,26 +3032,26 @@
       <c r="H85" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I85" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J85" s="25"/>
-    </row>
-    <row r="86">
+      <c r="I85" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" s="14"/>
+    </row>
+    <row r="86" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A86" s="7">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="B86" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C86" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D86" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E86" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" s="18">
+        <v>2</v>
+      </c>
+      <c r="E86" s="19">
+        <v>2</v>
       </c>
       <c r="F86" s="13" t="s">
         <v>12</v>
@@ -3092,26 +3062,26 @@
       <c r="H86" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I86" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" s="25"/>
-    </row>
-    <row r="87">
+      <c r="I86" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" s="14"/>
+    </row>
+    <row r="87" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A87" s="7">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="B87" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C87" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D87" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E87" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="18">
+        <v>4</v>
+      </c>
+      <c r="E87" s="19">
+        <v>2</v>
       </c>
       <c r="F87" s="13" t="s">
         <v>12</v>
@@ -3122,26 +3092,26 @@
       <c r="H87" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I87" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J87" s="25"/>
-    </row>
-    <row r="88">
+      <c r="I87" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" s="14"/>
+    </row>
+    <row r="88" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A88" s="7">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="B88" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C88" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E88" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="18">
+        <v>3</v>
+      </c>
+      <c r="E88" s="19">
+        <v>2</v>
       </c>
       <c r="F88" s="13" t="s">
         <v>10</v>
@@ -3152,26 +3122,26 @@
       <c r="H88" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I88" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J88" s="25"/>
-    </row>
-    <row r="89">
+      <c r="I88" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" s="14"/>
+    </row>
+    <row r="89" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A89" s="7">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="B89" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C89" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E89" s="23">
-        <v>3.0</v>
+        <v>4</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="18">
+        <v>4</v>
+      </c>
+      <c r="E89" s="19">
+        <v>3</v>
       </c>
       <c r="F89" s="13" t="s">
         <v>12</v>
@@ -3182,26 +3152,26 @@
       <c r="H89" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J89" s="25"/>
-    </row>
-    <row r="90">
+      <c r="I89" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" s="14"/>
+    </row>
+    <row r="90" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A90" s="7">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="B90" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C90" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E90" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="18">
+        <v>3</v>
+      </c>
+      <c r="E90" s="19">
+        <v>2</v>
       </c>
       <c r="F90" s="13" t="s">
         <v>10</v>
@@ -3212,26 +3182,26 @@
       <c r="H90" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I90" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J90" s="25"/>
-    </row>
-    <row r="91">
+      <c r="I90" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" s="14"/>
+    </row>
+    <row r="91" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A91" s="7">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="B91" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C91" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D91" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E91" s="23">
-        <v>3.0</v>
+        <v>4</v>
+      </c>
+      <c r="C91" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="18">
+        <v>4</v>
+      </c>
+      <c r="E91" s="19">
+        <v>3</v>
       </c>
       <c r="F91" s="13" t="s">
         <v>12</v>
@@ -3242,26 +3212,26 @@
       <c r="H91" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I91" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J91" s="25"/>
-    </row>
-    <row r="92">
+      <c r="I91" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" s="14"/>
+    </row>
+    <row r="92" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A92" s="7">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="B92" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C92" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D92" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E92" s="23">
-        <v>3.0</v>
+        <v>4</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="18">
+        <v>3</v>
+      </c>
+      <c r="E92" s="19">
+        <v>3</v>
       </c>
       <c r="F92" s="13" t="s">
         <v>12</v>
@@ -3272,26 +3242,26 @@
       <c r="H92" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I92" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J92" s="25"/>
-    </row>
-    <row r="93">
+      <c r="I92" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92" s="14"/>
+    </row>
+    <row r="93" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A93" s="7">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="B93" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C93" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D93" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E93" s="23">
-        <v>2.0</v>
+      <c r="D93" s="18">
+        <v>3</v>
+      </c>
+      <c r="E93" s="19">
+        <v>2</v>
       </c>
       <c r="F93" s="13" t="s">
         <v>10</v>
@@ -3302,26 +3272,26 @@
       <c r="H93" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I93" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" s="25"/>
-    </row>
-    <row r="94">
+      <c r="I93" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" s="14"/>
+    </row>
+    <row r="94" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A94" s="7">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="B94" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C94" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D94" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E94" s="23">
-        <v>2.0</v>
+      <c r="D94" s="18">
+        <v>3</v>
+      </c>
+      <c r="E94" s="19">
+        <v>2</v>
       </c>
       <c r="F94" s="13" t="s">
         <v>10</v>
@@ -3332,26 +3302,26 @@
       <c r="H94" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I94" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J94" s="25"/>
-    </row>
-    <row r="95">
+      <c r="I94" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" s="14"/>
+    </row>
+    <row r="95" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A95" s="7">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="B95" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C95" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E95" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C95" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="18">
+        <v>4</v>
+      </c>
+      <c r="E95" s="19">
+        <v>2</v>
       </c>
       <c r="F95" s="13" t="s">
         <v>12</v>
@@ -3362,26 +3332,26 @@
       <c r="H95" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I95" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J95" s="25"/>
-    </row>
-    <row r="96">
+      <c r="I95" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" s="14"/>
+    </row>
+    <row r="96" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A96" s="7">
-        <v>95.0</v>
+        <v>95</v>
       </c>
       <c r="B96" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C96" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E96" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="18">
+        <v>2</v>
+      </c>
+      <c r="E96" s="19">
+        <v>2</v>
       </c>
       <c r="F96" s="13" t="s">
         <v>12</v>
@@ -3392,26 +3362,26 @@
       <c r="H96" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I96" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J96" s="25"/>
-    </row>
-    <row r="97">
+      <c r="I96" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" s="14"/>
+    </row>
+    <row r="97" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A97" s="7">
-        <v>96.0</v>
+        <v>96</v>
       </c>
       <c r="B97" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C97" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D97" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E97" s="23">
-        <v>3.0</v>
+        <v>6</v>
+      </c>
+      <c r="C97" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" s="18">
+        <v>2</v>
+      </c>
+      <c r="E97" s="19">
+        <v>3</v>
       </c>
       <c r="F97" s="13" t="s">
         <v>10</v>
@@ -3422,26 +3392,26 @@
       <c r="H97" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I97" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J97" s="25"/>
-    </row>
-    <row r="98">
+      <c r="I97" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J97" s="14"/>
+    </row>
+    <row r="98" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A98" s="7">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="B98" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C98" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D98" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E98" s="23">
-        <v>2.0</v>
+      <c r="D98" s="18">
+        <v>2</v>
+      </c>
+      <c r="E98" s="19">
+        <v>2</v>
       </c>
       <c r="F98" s="13" t="s">
         <v>12</v>
@@ -3452,26 +3422,26 @@
       <c r="H98" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I98" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J98" s="25"/>
-    </row>
-    <row r="99">
+      <c r="I98" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J98" s="14"/>
+    </row>
+    <row r="99" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A99" s="7">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="B99" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C99" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E99" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C99" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="18">
+        <v>4</v>
+      </c>
+      <c r="E99" s="19">
+        <v>2</v>
       </c>
       <c r="F99" s="13" t="s">
         <v>12</v>
@@ -3482,26 +3452,26 @@
       <c r="H99" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I99" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J99" s="25"/>
-    </row>
-    <row r="100">
+      <c r="I99" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J99" s="14"/>
+    </row>
+    <row r="100" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A100" s="7">
-        <v>99.0</v>
+        <v>99</v>
       </c>
       <c r="B100" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C100" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D100" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E100" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C100" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="18">
+        <v>4</v>
+      </c>
+      <c r="E100" s="19">
+        <v>2</v>
       </c>
       <c r="F100" s="13" t="s">
         <v>12</v>
@@ -3512,26 +3482,26 @@
       <c r="H100" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I100" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J100" s="25"/>
-    </row>
-    <row r="101">
+      <c r="I100" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100" s="14"/>
+    </row>
+    <row r="101" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A101" s="7">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="B101" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C101" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D101" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E101" s="23">
-        <v>2.0</v>
+      <c r="D101" s="18">
+        <v>3</v>
+      </c>
+      <c r="E101" s="19">
+        <v>2</v>
       </c>
       <c r="F101" s="13" t="s">
         <v>12</v>
@@ -3542,24 +3512,24 @@
       <c r="H101" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I101" s="27"/>
-      <c r="J101" s="25"/>
-    </row>
-    <row r="102">
+      <c r="I101" s="22"/>
+      <c r="J101" s="14"/>
+    </row>
+    <row r="102" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A102" s="7">
-        <v>101.0</v>
+        <v>101</v>
       </c>
       <c r="B102" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C102" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D102" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E102" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C102" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" s="18">
+        <v>4</v>
+      </c>
+      <c r="E102" s="19">
+        <v>2</v>
       </c>
       <c r="F102" s="13" t="s">
         <v>10</v>
@@ -3570,26 +3540,26 @@
       <c r="H102" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I102" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J102" s="25"/>
-    </row>
-    <row r="103">
+      <c r="I102" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J102" s="14"/>
+    </row>
+    <row r="103" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A103" s="7">
-        <v>102.0</v>
+        <v>102</v>
       </c>
       <c r="B103" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C103" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D103" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E103" s="23">
-        <v>2.0</v>
+      <c r="D103" s="18">
+        <v>3</v>
+      </c>
+      <c r="E103" s="19">
+        <v>2</v>
       </c>
       <c r="F103" s="13" t="s">
         <v>12</v>
@@ -3600,26 +3570,26 @@
       <c r="H103" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I103" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J103" s="25"/>
-    </row>
-    <row r="104">
+      <c r="I103" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J103" s="14"/>
+    </row>
+    <row r="104" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A104" s="7">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="B104" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C104" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D104" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E104" s="23">
-        <v>3.0</v>
+      <c r="D104" s="18">
+        <v>4</v>
+      </c>
+      <c r="E104" s="19">
+        <v>3</v>
       </c>
       <c r="F104" s="13" t="s">
         <v>10</v>
@@ -3630,26 +3600,26 @@
       <c r="H104" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I104" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J104" s="25"/>
-    </row>
-    <row r="105">
+      <c r="I104" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104" s="14"/>
+    </row>
+    <row r="105" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A105" s="7">
-        <v>104.0</v>
+        <v>104</v>
       </c>
       <c r="B105" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C105" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D105" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E105" s="23">
-        <v>2.0</v>
+      <c r="D105" s="18">
+        <v>4</v>
+      </c>
+      <c r="E105" s="19">
+        <v>2</v>
       </c>
       <c r="F105" s="13" t="s">
         <v>12</v>
@@ -3660,26 +3630,26 @@
       <c r="H105" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I105" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J105" s="25"/>
-    </row>
-    <row r="106">
+      <c r="I105" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" s="14"/>
+    </row>
+    <row r="106" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A106" s="7">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="B106" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C106" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D106" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E106" s="23">
-        <v>2.0</v>
+      <c r="D106" s="18">
+        <v>3</v>
+      </c>
+      <c r="E106" s="19">
+        <v>2</v>
       </c>
       <c r="F106" s="13" t="s">
         <v>10</v>
@@ -3690,26 +3660,26 @@
       <c r="H106" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I106" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J106" s="25"/>
-    </row>
-    <row r="107">
+      <c r="I106" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" s="14"/>
+    </row>
+    <row r="107" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A107" s="7">
-        <v>106.0</v>
+        <v>106</v>
       </c>
       <c r="B107" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C107" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D107" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E107" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C107" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="18">
+        <v>3</v>
+      </c>
+      <c r="E107" s="19">
+        <v>2</v>
       </c>
       <c r="F107" s="13" t="s">
         <v>10</v>
@@ -3720,26 +3690,26 @@
       <c r="H107" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I107" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J107" s="25"/>
-    </row>
-    <row r="108">
+      <c r="I107" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J107" s="14"/>
+    </row>
+    <row r="108" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A108" s="7">
-        <v>107.0</v>
+        <v>107</v>
       </c>
       <c r="B108" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C108" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D108" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E108" s="23">
-        <v>1.0</v>
+        <v>4</v>
+      </c>
+      <c r="C108" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="18">
+        <v>2</v>
+      </c>
+      <c r="E108" s="19">
+        <v>1</v>
       </c>
       <c r="F108" s="13" t="s">
         <v>12</v>
@@ -3750,26 +3720,26 @@
       <c r="H108" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I108" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J108" s="25"/>
-    </row>
-    <row r="109">
+      <c r="I108" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J108" s="14"/>
+    </row>
+    <row r="109" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A109" s="7">
-        <v>108.0</v>
+        <v>108</v>
       </c>
       <c r="B109" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C109" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E109" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C109" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="18">
+        <v>2</v>
+      </c>
+      <c r="E109" s="19">
+        <v>2</v>
       </c>
       <c r="F109" s="13" t="s">
         <v>10</v>
@@ -3780,26 +3750,26 @@
       <c r="H109" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I109" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J109" s="25"/>
-    </row>
-    <row r="110">
+      <c r="I109" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J109" s="14"/>
+    </row>
+    <row r="110" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A110" s="7">
-        <v>109.0</v>
+        <v>109</v>
       </c>
       <c r="B110" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C110" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D110" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E110" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C110" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="18">
+        <v>3</v>
+      </c>
+      <c r="E110" s="19">
+        <v>2</v>
       </c>
       <c r="F110" s="13" t="s">
         <v>10</v>
@@ -3810,26 +3780,26 @@
       <c r="H110" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I110" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J110" s="25"/>
-    </row>
-    <row r="111">
+      <c r="I110" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J110" s="14"/>
+    </row>
+    <row r="111" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A111" s="7">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="B111" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C111" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D111" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E111" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C111" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="18">
+        <v>3</v>
+      </c>
+      <c r="E111" s="19">
+        <v>2</v>
       </c>
       <c r="F111" s="13" t="s">
         <v>10</v>
@@ -3840,26 +3810,26 @@
       <c r="H111" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I111" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J111" s="25"/>
-    </row>
-    <row r="112">
+      <c r="I111" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J111" s="14"/>
+    </row>
+    <row r="112" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A112" s="7">
-        <v>111.0</v>
+        <v>111</v>
       </c>
       <c r="B112" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C112" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E112" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C112" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="18">
+        <v>4</v>
+      </c>
+      <c r="E112" s="19">
+        <v>2</v>
       </c>
       <c r="F112" s="13" t="s">
         <v>10</v>
@@ -3870,26 +3840,26 @@
       <c r="H112" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I112" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J112" s="25"/>
-    </row>
-    <row r="113">
+      <c r="I112" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J112" s="14"/>
+    </row>
+    <row r="113" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A113" s="7">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="B113" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C113" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D113" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E113" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="18">
+        <v>3</v>
+      </c>
+      <c r="E113" s="19">
+        <v>2</v>
       </c>
       <c r="F113" s="13" t="s">
         <v>10</v>
@@ -3900,26 +3870,26 @@
       <c r="H113" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I113" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J113" s="25"/>
-    </row>
-    <row r="114">
+      <c r="I113" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J113" s="14"/>
+    </row>
+    <row r="114" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A114" s="7">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="B114" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C114" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D114" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E114" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C114" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="18">
+        <v>2</v>
+      </c>
+      <c r="E114" s="19">
+        <v>2</v>
       </c>
       <c r="F114" s="13" t="s">
         <v>12</v>
@@ -3930,26 +3900,26 @@
       <c r="H114" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I114" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J114" s="25"/>
-    </row>
-    <row r="115">
+      <c r="I114" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J114" s="14"/>
+    </row>
+    <row r="115" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A115" s="7">
-        <v>114.0</v>
+        <v>114</v>
       </c>
       <c r="B115" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C115" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D115" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E115" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C115" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="18">
+        <v>3</v>
+      </c>
+      <c r="E115" s="19">
+        <v>2</v>
       </c>
       <c r="F115" s="13" t="s">
         <v>12</v>
@@ -3960,26 +3930,26 @@
       <c r="H115" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I115" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J115" s="25"/>
-    </row>
-    <row r="116">
+      <c r="I115" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J115" s="14"/>
+    </row>
+    <row r="116" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A116" s="7">
-        <v>115.0</v>
+        <v>115</v>
       </c>
       <c r="B116" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="C116" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E116" s="23">
-        <v>2.0</v>
+        <v>4</v>
+      </c>
+      <c r="C116" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="18">
+        <v>4</v>
+      </c>
+      <c r="E116" s="19">
+        <v>2</v>
       </c>
       <c r="F116" s="13" t="s">
         <v>12</v>
@@ -3990,26 +3960,26 @@
       <c r="H116" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I116" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J116" s="25"/>
-    </row>
-    <row r="117">
+      <c r="I116" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J116" s="14"/>
+    </row>
+    <row r="117" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A117" s="7">
-        <v>116.0</v>
+        <v>116</v>
       </c>
       <c r="B117" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C117" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D117" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E117" s="23">
-        <v>3.0</v>
+        <v>6</v>
+      </c>
+      <c r="C117" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="18">
+        <v>4</v>
+      </c>
+      <c r="E117" s="19">
+        <v>3</v>
       </c>
       <c r="F117" s="13" t="s">
         <v>10</v>
@@ -4020,26 +3990,26 @@
       <c r="H117" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I117" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J117" s="25"/>
-    </row>
-    <row r="118">
+      <c r="I117" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J117" s="14"/>
+    </row>
+    <row r="118" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A118" s="7">
-        <v>117.0</v>
+        <v>117</v>
       </c>
       <c r="B118" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C118" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D118" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E118" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C118" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="18">
+        <v>3</v>
+      </c>
+      <c r="E118" s="19">
+        <v>2</v>
       </c>
       <c r="F118" s="13" t="s">
         <v>10</v>
@@ -4050,26 +4020,26 @@
       <c r="H118" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I118" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J118" s="25"/>
-    </row>
-    <row r="119">
+      <c r="I118" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J118" s="14"/>
+    </row>
+    <row r="119" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A119" s="7">
-        <v>118.0</v>
+        <v>118</v>
       </c>
       <c r="B119" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C119" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D119" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E119" s="23">
-        <v>2.0</v>
+        <v>7</v>
+      </c>
+      <c r="C119" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119" s="18">
+        <v>4</v>
+      </c>
+      <c r="E119" s="19">
+        <v>2</v>
       </c>
       <c r="F119" s="13" t="s">
         <v>12</v>
@@ -4080,26 +4050,26 @@
       <c r="H119" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I119" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J119" s="25"/>
-    </row>
-    <row r="120">
+      <c r="I119" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J119" s="14"/>
+    </row>
+    <row r="120" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A120" s="7">
-        <v>119.0</v>
+        <v>119</v>
       </c>
       <c r="B120" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="C120" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D120" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E120" s="23">
-        <v>2.0</v>
+      <c r="D120" s="18">
+        <v>2</v>
+      </c>
+      <c r="E120" s="19">
+        <v>2</v>
       </c>
       <c r="F120" s="13" t="s">
         <v>10</v>
@@ -4110,26 +4080,26 @@
       <c r="H120" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I120" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J120" s="25"/>
-    </row>
-    <row r="121">
+      <c r="I120" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J120" s="14"/>
+    </row>
+    <row r="121" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A121" s="7">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="B121" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="C121" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D121" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E121" s="23">
-        <v>1.0</v>
+        <v>5</v>
+      </c>
+      <c r="C121" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="18">
+        <v>2</v>
+      </c>
+      <c r="E121" s="19">
+        <v>1</v>
       </c>
       <c r="F121" s="13" t="s">
         <v>12</v>
@@ -4140,26 +4110,26 @@
       <c r="H121" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I121" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J121" s="25"/>
-    </row>
-    <row r="122">
+      <c r="I121" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J121" s="14"/>
+    </row>
+    <row r="122" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A122" s="7">
-        <v>121.0</v>
+        <v>121</v>
       </c>
       <c r="B122" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="C122" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D122" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E122" s="23">
-        <v>2.0</v>
+        <v>5</v>
+      </c>
+      <c r="C122" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D122" s="18">
+        <v>2</v>
+      </c>
+      <c r="E122" s="19">
+        <v>2</v>
       </c>
       <c r="F122" s="13" t="s">
         <v>12</v>
@@ -4170,26 +4140,26 @@
       <c r="H122" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I122" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J122" s="25"/>
-    </row>
-    <row r="123">
+      <c r="I122" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J122" s="14"/>
+    </row>
+    <row r="123" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A123" s="7">
-        <v>122.0</v>
+        <v>122</v>
       </c>
       <c r="B123" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="C123" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D123" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E123" s="23">
-        <v>2.0</v>
+        <v>5</v>
+      </c>
+      <c r="C123" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" s="18">
+        <v>2</v>
+      </c>
+      <c r="E123" s="19">
+        <v>2</v>
       </c>
       <c r="F123" s="13" t="s">
         <v>10</v>
@@ -4200,26 +4170,26 @@
       <c r="H123" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I123" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J123" s="25"/>
-    </row>
-    <row r="124">
+      <c r="I123" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J123" s="14"/>
+    </row>
+    <row r="124" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A124" s="7">
-        <v>123.0</v>
+        <v>123</v>
       </c>
       <c r="B124" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C124" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D124" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E124" s="23">
-        <v>2.0</v>
+      <c r="D124" s="18">
+        <v>2</v>
+      </c>
+      <c r="E124" s="19">
+        <v>2</v>
       </c>
       <c r="F124" s="13" t="s">
         <v>12</v>
@@ -4230,26 +4200,26 @@
       <c r="H124" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I124" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J124" s="25"/>
-    </row>
-    <row r="125">
+      <c r="I124" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J124" s="14"/>
+    </row>
+    <row r="125" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A125" s="7">
-        <v>124.0</v>
+        <v>124</v>
       </c>
       <c r="B125" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="C125" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D125" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E125" s="23">
-        <v>2.0</v>
+        <v>5</v>
+      </c>
+      <c r="C125" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="18">
+        <v>2</v>
+      </c>
+      <c r="E125" s="19">
+        <v>2</v>
       </c>
       <c r="F125" s="13" t="s">
         <v>10</v>
@@ -4260,26 +4230,26 @@
       <c r="H125" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I125" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J125" s="25"/>
-    </row>
-    <row r="126">
+      <c r="I125" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J125" s="14"/>
+    </row>
+    <row r="126" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A126" s="7">
-        <v>125.0</v>
+        <v>125</v>
       </c>
       <c r="B126" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C126" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D126" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E126" s="23">
-        <v>2.0</v>
+        <v>7</v>
+      </c>
+      <c r="C126" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="18">
+        <v>3</v>
+      </c>
+      <c r="E126" s="19">
+        <v>2</v>
       </c>
       <c r="F126" s="13" t="s">
         <v>12</v>
@@ -4290,26 +4260,26 @@
       <c r="H126" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I126" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J126" s="25"/>
-    </row>
-    <row r="127">
+      <c r="I126" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J126" s="14"/>
+    </row>
+    <row r="127" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A127" s="7">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="B127" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="C127" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D127" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E127" s="23">
-        <v>2.0</v>
+        <v>5</v>
+      </c>
+      <c r="C127" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="18">
+        <v>3</v>
+      </c>
+      <c r="E127" s="19">
+        <v>2</v>
       </c>
       <c r="F127" s="13" t="s">
         <v>12</v>
@@ -4320,26 +4290,26 @@
       <c r="H127" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I127" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J127" s="25"/>
-    </row>
-    <row r="128">
+      <c r="I127" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J127" s="14"/>
+    </row>
+    <row r="128" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A128" s="7">
-        <v>127.0</v>
+        <v>127</v>
       </c>
       <c r="B128" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C128" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D128" s="22">
-        <v>6.0</v>
-      </c>
-      <c r="E128" s="23">
-        <v>3.0</v>
+        <v>9</v>
+      </c>
+      <c r="C128" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="18">
+        <v>6</v>
+      </c>
+      <c r="E128" s="19">
+        <v>3</v>
       </c>
       <c r="F128" s="13" t="s">
         <v>12</v>
@@ -4350,26 +4320,26 @@
       <c r="H128" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I128" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J128" s="25"/>
-    </row>
-    <row r="129">
+      <c r="I128" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J128" s="14"/>
+    </row>
+    <row r="129" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A129" s="7">
-        <v>128.0</v>
+        <v>128</v>
       </c>
       <c r="B129" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C129" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D129" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E129" s="23">
-        <v>3.0</v>
+      <c r="D129" s="18">
+        <v>3</v>
+      </c>
+      <c r="E129" s="19">
+        <v>3</v>
       </c>
       <c r="F129" s="13" t="s">
         <v>12</v>
@@ -4380,26 +4350,26 @@
       <c r="H129" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I129" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J129" s="25"/>
-    </row>
-    <row r="130">
+      <c r="I129" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J129" s="14"/>
+    </row>
+    <row r="130" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A130" s="7">
-        <v>129.0</v>
+        <v>129</v>
       </c>
       <c r="B130" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C130" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D130" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E130" s="23">
-        <v>2.0</v>
+        <v>9</v>
+      </c>
+      <c r="C130" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="18">
+        <v>2</v>
+      </c>
+      <c r="E130" s="19">
+        <v>2</v>
       </c>
       <c r="F130" s="13" t="s">
         <v>12</v>
@@ -4410,26 +4380,26 @@
       <c r="H130" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I130" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J130" s="25"/>
-    </row>
-    <row r="131">
+      <c r="I130" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J130" s="14"/>
+    </row>
+    <row r="131" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A131" s="7">
-        <v>130.0</v>
+        <v>130</v>
       </c>
       <c r="B131" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C131" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D131" s="22">
-        <v>4.0</v>
-      </c>
-      <c r="E131" s="23">
-        <v>3.0</v>
+        <v>7</v>
+      </c>
+      <c r="C131" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="18">
+        <v>4</v>
+      </c>
+      <c r="E131" s="19">
+        <v>3</v>
       </c>
       <c r="F131" s="13" t="s">
         <v>12</v>
@@ -4440,26 +4410,26 @@
       <c r="H131" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I131" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J131" s="25"/>
-    </row>
-    <row r="132">
+      <c r="I131" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J131" s="14"/>
+    </row>
+    <row r="132" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A132" s="7">
-        <v>131.0</v>
+        <v>131</v>
       </c>
       <c r="B132" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C132" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D132" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E132" s="23">
-        <v>3.0</v>
+        <v>9</v>
+      </c>
+      <c r="C132" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" s="18">
+        <v>3</v>
+      </c>
+      <c r="E132" s="19">
+        <v>3</v>
       </c>
       <c r="F132" s="13" t="s">
         <v>12</v>
@@ -4470,26 +4440,26 @@
       <c r="H132" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I132" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J132" s="25"/>
-    </row>
-    <row r="133">
+      <c r="I132" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J132" s="14"/>
+    </row>
+    <row r="133" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A133" s="7">
-        <v>132.0</v>
+        <v>132</v>
       </c>
       <c r="B133" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C133" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D133" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E133" s="23">
-        <v>2.0</v>
+        <v>7</v>
+      </c>
+      <c r="C133" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" s="18">
+        <v>2</v>
+      </c>
+      <c r="E133" s="19">
+        <v>2</v>
       </c>
       <c r="F133" s="13" t="s">
         <v>10</v>
@@ -4500,26 +4470,26 @@
       <c r="H133" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I133" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J133" s="25"/>
-    </row>
-    <row r="134">
+      <c r="I133" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J133" s="14"/>
+    </row>
+    <row r="134" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A134" s="7">
-        <v>133.0</v>
+        <v>133</v>
       </c>
       <c r="B134" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C134" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D134" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E134" s="23">
-        <v>3.0</v>
+        <v>9</v>
+      </c>
+      <c r="C134" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="18">
+        <v>3</v>
+      </c>
+      <c r="E134" s="19">
+        <v>3</v>
       </c>
       <c r="F134" s="13" t="s">
         <v>10</v>
@@ -4530,26 +4500,26 @@
       <c r="H134" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I134" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J134" s="25"/>
-    </row>
-    <row r="135">
+      <c r="I134" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J134" s="14"/>
+    </row>
+    <row r="135" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A135" s="7">
-        <v>134.0</v>
+        <v>134</v>
       </c>
       <c r="B135" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C135" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D135" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E135" s="23">
-        <v>3.0</v>
+        <v>7</v>
+      </c>
+      <c r="C135" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="18">
+        <v>3</v>
+      </c>
+      <c r="E135" s="19">
+        <v>3</v>
       </c>
       <c r="F135" s="13" t="s">
         <v>12</v>
@@ -4560,26 +4530,26 @@
       <c r="H135" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I135" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J135" s="25"/>
-    </row>
-    <row r="136">
+      <c r="I135" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J135" s="14"/>
+    </row>
+    <row r="136" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A136" s="7">
-        <v>135.0</v>
+        <v>135</v>
       </c>
       <c r="B136" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="C136" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D136" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E136" s="23">
-        <v>2.0</v>
+        <v>5</v>
+      </c>
+      <c r="C136" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="18">
+        <v>3</v>
+      </c>
+      <c r="E136" s="19">
+        <v>2</v>
       </c>
       <c r="F136" s="13" t="s">
         <v>10</v>
@@ -4590,26 +4560,26 @@
       <c r="H136" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I136" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J136" s="25"/>
-    </row>
-    <row r="137">
+      <c r="I136" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J136" s="14"/>
+    </row>
+    <row r="137" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A137" s="7">
-        <v>136.0</v>
+        <v>136</v>
       </c>
       <c r="B137" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C137" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D137" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E137" s="23">
-        <v>2.0</v>
+        <v>7</v>
+      </c>
+      <c r="C137" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" s="18">
+        <v>3</v>
+      </c>
+      <c r="E137" s="19">
+        <v>2</v>
       </c>
       <c r="F137" s="13" t="s">
         <v>10</v>
@@ -4620,26 +4590,26 @@
       <c r="H137" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I137" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J137" s="25"/>
-    </row>
-    <row r="138">
+      <c r="I137" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J137" s="14"/>
+    </row>
+    <row r="138" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A138" s="7">
-        <v>137.0</v>
+        <v>137</v>
       </c>
       <c r="B138" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C138" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D138" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E138" s="23">
-        <v>2.0</v>
+        <v>9</v>
+      </c>
+      <c r="C138" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="18">
+        <v>2</v>
+      </c>
+      <c r="E138" s="19">
+        <v>2</v>
       </c>
       <c r="F138" s="13" t="s">
         <v>10</v>
@@ -4650,26 +4620,26 @@
       <c r="H138" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I138" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J138" s="25"/>
-    </row>
-    <row r="139">
+      <c r="I138" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J138" s="14"/>
+    </row>
+    <row r="139" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A139" s="7">
-        <v>138.0</v>
+        <v>138</v>
       </c>
       <c r="B139" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C139" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D139" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E139" s="23">
-        <v>2.0</v>
+      <c r="D139" s="18">
+        <v>2</v>
+      </c>
+      <c r="E139" s="19">
+        <v>2</v>
       </c>
       <c r="F139" s="13" t="s">
         <v>12</v>
@@ -4680,26 +4650,26 @@
       <c r="H139" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I139" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J139" s="25"/>
-    </row>
-    <row r="140">
+      <c r="I139" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J139" s="14"/>
+    </row>
+    <row r="140" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A140" s="7">
-        <v>139.0</v>
+        <v>139</v>
       </c>
       <c r="B140" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C140" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D140" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E140" s="23">
-        <v>2.0</v>
+        <v>9</v>
+      </c>
+      <c r="C140" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="18">
+        <v>3</v>
+      </c>
+      <c r="E140" s="19">
+        <v>2</v>
       </c>
       <c r="F140" s="13" t="s">
         <v>10</v>
@@ -4710,26 +4680,26 @@
       <c r="H140" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I140" s="24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J140" s="25"/>
-    </row>
-    <row r="141">
+      <c r="I140" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J140" s="14"/>
+    </row>
+    <row r="141" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A141" s="7">
-        <v>140.0</v>
+        <v>140</v>
       </c>
       <c r="B141" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C141" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D141" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E141" s="23">
-        <v>2.0</v>
+        <v>9</v>
+      </c>
+      <c r="C141" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D141" s="18">
+        <v>2</v>
+      </c>
+      <c r="E141" s="19">
+        <v>2</v>
       </c>
       <c r="F141" s="13" t="s">
         <v>12</v>
@@ -4740,26 +4710,26 @@
       <c r="H141" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I141" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J141" s="25"/>
-    </row>
-    <row r="142">
+      <c r="I141" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J141" s="14"/>
+    </row>
+    <row r="142" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A142" s="7">
-        <v>141.0</v>
+        <v>141</v>
       </c>
       <c r="B142" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C142" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D142" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E142" s="23">
-        <v>2.0</v>
+        <v>7</v>
+      </c>
+      <c r="C142" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="18">
+        <v>3</v>
+      </c>
+      <c r="E142" s="19">
+        <v>2</v>
       </c>
       <c r="F142" s="13" t="s">
         <v>10</v>
@@ -4770,26 +4740,26 @@
       <c r="H142" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I142" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J142" s="25"/>
-    </row>
-    <row r="143">
+      <c r="I142" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J142" s="14"/>
+    </row>
+    <row r="143" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A143" s="7">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="B143" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C143" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D143" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E143" s="23">
-        <v>2.0</v>
+        <v>9</v>
+      </c>
+      <c r="C143" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="18">
+        <v>3</v>
+      </c>
+      <c r="E143" s="19">
+        <v>2</v>
       </c>
       <c r="F143" s="13" t="s">
         <v>12</v>
@@ -4800,26 +4770,26 @@
       <c r="H143" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I143" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J143" s="25"/>
-    </row>
-    <row r="144">
+      <c r="I143" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J143" s="14"/>
+    </row>
+    <row r="144" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A144" s="7">
-        <v>143.0</v>
+        <v>143</v>
       </c>
       <c r="B144" s="7">
-        <v>7.0</v>
-      </c>
-      <c r="C144" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D144" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E144" s="23">
-        <v>2.0</v>
+        <v>7</v>
+      </c>
+      <c r="C144" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D144" s="18">
+        <v>2</v>
+      </c>
+      <c r="E144" s="19">
+        <v>2</v>
       </c>
       <c r="F144" s="13" t="s">
         <v>12</v>
@@ -4830,26 +4800,26 @@
       <c r="H144" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I144" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J144" s="25"/>
-    </row>
-    <row r="145">
+      <c r="I144" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J144" s="14"/>
+    </row>
+    <row r="145" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A145" s="7">
-        <v>144.0</v>
+        <v>144</v>
       </c>
       <c r="B145" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="C145" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D145" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E145" s="23">
-        <v>2.0</v>
+        <v>9</v>
+      </c>
+      <c r="C145" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D145" s="18">
+        <v>2</v>
+      </c>
+      <c r="E145" s="19">
+        <v>2</v>
       </c>
       <c r="F145" s="13" t="s">
         <v>10</v>
@@ -4860,26 +4830,26 @@
       <c r="H145" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I145" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J145" s="25"/>
-    </row>
-    <row r="146">
+      <c r="I145" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J145" s="14"/>
+    </row>
+    <row r="146" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A146" s="7">
-        <v>145.0</v>
+        <v>145</v>
       </c>
       <c r="B146" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C146" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D146" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E146" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C146" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146" s="18">
+        <v>2</v>
+      </c>
+      <c r="E146" s="19">
+        <v>2</v>
       </c>
       <c r="F146" s="13" t="s">
         <v>10</v>
@@ -4890,26 +4860,26 @@
       <c r="H146" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I146" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J146" s="25"/>
-    </row>
-    <row r="147">
+      <c r="I146" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J146" s="14"/>
+    </row>
+    <row r="147" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A147" s="7">
-        <v>146.0</v>
+        <v>146</v>
       </c>
       <c r="B147" s="7">
-        <v>8.0</v>
-      </c>
-      <c r="C147" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C147" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D147" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E147" s="23">
-        <v>2.0</v>
+      <c r="D147" s="18">
+        <v>3</v>
+      </c>
+      <c r="E147" s="19">
+        <v>2</v>
       </c>
       <c r="F147" s="13" t="s">
         <v>10</v>
@@ -4920,26 +4890,26 @@
       <c r="H147" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I147" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J147" s="25"/>
-    </row>
-    <row r="148">
+      <c r="I147" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J147" s="14"/>
+    </row>
+    <row r="148" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A148" s="7">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="B148" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C148" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D148" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="E148" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C148" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="18">
+        <v>2</v>
+      </c>
+      <c r="E148" s="19">
+        <v>2</v>
       </c>
       <c r="F148" s="13" t="s">
         <v>12</v>
@@ -4950,26 +4920,26 @@
       <c r="H148" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I148" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J148" s="25"/>
-    </row>
-    <row r="149">
+      <c r="I148" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J148" s="14"/>
+    </row>
+    <row r="149" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="A149" s="7">
-        <v>148.0</v>
+        <v>148</v>
       </c>
       <c r="B149" s="7">
-        <v>6.0</v>
-      </c>
-      <c r="C149" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D149" s="22">
-        <v>3.0</v>
-      </c>
-      <c r="E149" s="23">
-        <v>2.0</v>
+        <v>6</v>
+      </c>
+      <c r="C149" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" s="18">
+        <v>3</v>
+      </c>
+      <c r="E149" s="19">
+        <v>2</v>
       </c>
       <c r="F149" s="13" t="s">
         <v>12</v>
@@ -4980,15 +4950,15 @@
       <c r="H149" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I149" s="26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J149" s="25"/>
+      <c r="I149" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J149" s="14"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>